--- a/data/trans_orig/P05B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05B_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23444</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30569</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>48210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>669623</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>684789</t>
+          <t>684793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>657782</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>675017</t>
+          <t>675400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1333514</t>
+          <t>1333208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1356505</t>
+          <t>1356848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33044</t>
+          <t>34817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57040</t>
+          <t>56997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50341</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83280</t>
+          <t>83216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>928756</t>
+          <t>926983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>947598</t>
+          <t>946714</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>909729</t>
+          <t>909772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>935246</t>
+          <t>935093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1845289</t>
+          <t>1845353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1878228</t>
+          <t>1878261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28086</t>
+          <t>27522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18049</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30645</t>
+          <t>31499</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58383</t>
+          <t>58010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>650423</t>
+          <t>650987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669416</t>
+          <t>669457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645052</t>
+          <t>645402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665792</t>
+          <t>665800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303967</t>
+          <t>1304340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1331705</t>
+          <t>1330851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57966</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53979</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85739</t>
+          <t>87031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93399</t>
+          <t>91060</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132642</t>
+          <t>132838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>881082</t>
+          <t>881225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>906718</t>
+          <t>907865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>952873</t>
+          <t>951581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>984633</t>
+          <t>984019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1845018</t>
+          <t>1844822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1884261</t>
+          <t>1886600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>79226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118038</t>
+          <t>119159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135783</t>
+          <t>135032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183332</t>
+          <t>183299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>224001</t>
+          <t>225037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>289091</t>
+          <t>289010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3154386</t>
+          <t>3153265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3194603</t>
+          <t>3193198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3194241</t>
+          <t>3194274</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3241790</t>
+          <t>3242541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6360906</t>
+          <t>6360987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6425996</t>
+          <t>6424960</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1682</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>696975</t>
+          <t>697329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>687133</t>
+          <t>687225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>693942</t>
+          <t>693946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1387082</t>
+          <t>1388247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1396605</t>
+          <t>1396663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27444</t>
+          <t>26767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17791</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>31358</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57212</t>
+          <t>58747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>986551</t>
+          <t>987228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1004832</t>
+          <t>1004637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>988424</t>
+          <t>989768</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1010125</t>
+          <t>1010360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1984698</t>
+          <t>1983163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2011684</t>
+          <t>2010552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26950</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16353</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>36809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>730673</t>
+          <t>729056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>748656</t>
+          <t>748419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>758621</t>
+          <t>758663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770944</t>
+          <t>770961</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1497174</t>
+          <t>1495789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1517438</t>
+          <t>1516922</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34015</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13378</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32491</t>
+          <t>29796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57315</t>
+          <t>57136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903700</t>
+          <t>903157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923327</t>
+          <t>923860</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1011331</t>
+          <t>1014026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030444</t>
+          <t>1032066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1924221</t>
+          <t>1924400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1950655</t>
+          <t>1951484</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42992</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73995</t>
+          <t>72273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42825</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73961</t>
+          <t>74619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93701</t>
+          <t>94193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137168</t>
+          <t>141390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3338807</t>
+          <t>3340529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3369810</t>
+          <t>3370708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3467626</t>
+          <t>3466968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3498762</t>
+          <t>3498440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6817221</t>
+          <t>6812999</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6860688</t>
+          <t>6860196</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18636</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21115</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>654684</t>
+          <t>656096</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669132</t>
+          <t>669456</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>662062</t>
+          <t>661326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>670061</t>
+          <t>670064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323169</t>
+          <t>1323340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1338226</t>
+          <t>1337855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27736</t>
+          <t>26812</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43444</t>
+          <t>43988</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1000277</t>
+          <t>999819</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014814</t>
+          <t>1015195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012199</t>
+          <t>1013123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1029426</t>
+          <t>1029795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2017839</t>
+          <t>2017295</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2041762</t>
+          <t>2041870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22195</t>
+          <t>20680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26779</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51429</t>
+          <t>52488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>736311</t>
+          <t>737826</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752268</t>
+          <t>752239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>743896</t>
+          <t>743652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>765958</t>
+          <t>765554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1489875</t>
+          <t>1488816</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1514525</t>
+          <t>1513852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>39482</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>28771</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57752</t>
+          <t>56132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911482</t>
+          <t>909917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925840</t>
+          <t>925396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>994916</t>
+          <t>997333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1018088</t>
+          <t>1018203</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1911524</t>
+          <t>1913144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1938270</t>
+          <t>1940505</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33487</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62825</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59492</t>
+          <t>58836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97187</t>
+          <t>94563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100222</t>
+          <t>100422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145077</t>
+          <t>147346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3322810</t>
+          <t>3324342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3352148</t>
+          <t>3352559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3433326</t>
+          <t>3435950</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3471021</t>
+          <t>3471677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6771071</t>
+          <t>6768802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6815926</t>
+          <t>6815726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,17 +6604,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7775</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -6682,27 +6682,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>633020</t>
+          <t>688167</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>629508</t>
+          <t>684441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6717,17 +6717,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>722906</t>
+          <t>731740</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>720520</t>
+          <t>729301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>724295</t>
+          <t>733085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6752,17 +6752,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1355926</t>
+          <t>1419906</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351690</t>
+          <t>1415630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1357907</t>
+          <t>1421909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>733782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>733782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>724939</t>
+          <t>733782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1359361</t>
+          <t>1423405</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1359361</t>
+          <t>1423405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1359361</t>
+          <t>1423405</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11289</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1185291</t>
+          <t>1041528</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1177816</t>
+          <t>1034776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1188796</t>
+          <t>1044680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>950937</t>
+          <t>1063375</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>944280</t>
+          <t>1057928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>954248</t>
+          <t>1066857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2136228</t>
+          <t>2104903</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2128096</t>
+          <t>2096965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2141675</t>
+          <t>2109226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1189982</t>
+          <t>1046094</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1189982</t>
+          <t>1046094</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1189982</t>
+          <t>1046094</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957456</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957456</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957456</t>
+          <t>1070098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2147438</t>
+          <t>2116192</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2147438</t>
+          <t>2116192</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2147438</t>
+          <t>2116192</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,67 +7255,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10949</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1331</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7569</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2808</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7074</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>16518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -7368,69 +7368,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>699912</t>
+          <t>796367</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692963</t>
+          <t>789272</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>702808</t>
+          <t>799860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>808829</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>804690</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>810928</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1042</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>930558</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>926292</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>932737</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,93%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1712</t>
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1630469</t>
+          <t>1605195</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1622210</t>
+          <t>1596941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1634562</t>
+          <t>1609312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703912</t>
+          <t>801201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637277</t>
+          <t>1613459</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637277</t>
+          <t>1613459</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637277</t>
+          <t>1613459</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>39410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34053</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24015</t>
+          <t>25532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45866</t>
+          <t>45280</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61125</t>
+          <t>62420</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>49051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77920</t>
+          <t>81223</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>898963</t>
+          <t>960788</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885983</t>
+          <t>948389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908624</t>
+          <t>969971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1054260</t>
+          <t>1076157</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1042447</t>
+          <t>1066287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1064298</t>
+          <t>1086035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,22 +7781,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1953222</t>
+          <t>2036947</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1936427</t>
+          <t>2018144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967187</t>
+          <t>2050316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926034</t>
+          <t>987799</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926034</t>
+          <t>987799</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926034</t>
+          <t>987799</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1088313</t>
+          <t>1111567</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1088313</t>
+          <t>1111567</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1088313</t>
+          <t>1111567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2014347</t>
+          <t>2099367</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2014347</t>
+          <t>2099367</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2014347</t>
+          <t>2099367</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55549</t>
+          <t>53861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59068</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65425</t>
+          <t>68745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101869</t>
+          <t>103457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3417184</t>
+          <t>3486850</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3398800</t>
+          <t>3470857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3428620</t>
+          <t>3496648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3658661</t>
+          <t>3680101</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3645006</t>
+          <t>3667311</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3670348</t>
+          <t>3690909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7075845</t>
+          <t>7166951</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7056554</t>
+          <t>7148967</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7092998</t>
+          <t>7183679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454349</t>
+          <t>3524718</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3704074</t>
+          <t>3727706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7158423</t>
+          <t>7252424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
